--- a/Result/profitability/2010.xlsx
+++ b/Result/profitability/2010.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.39</v>
       </c>
       <c r="M2" t="n">
-        <v>0.53</v>
+        <v>0.56875</v>
       </c>
       <c r="N2" t="n">
-        <v>10.15625</v>
+        <v>10.63375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5975</v>
+        <v>0.63375</v>
       </c>
       <c r="N3" t="n">
-        <v>10.61875</v>
+        <v>11.0825</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.76</v>
       </c>
       <c r="M4" t="n">
-        <v>0.63125</v>
+        <v>0.6587499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>11.05625</v>
+        <v>11.15375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3762500000000001</v>
+        <v>0.3987499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>6.885</v>
+        <v>7.1625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2475</v>
+        <v>0.27375</v>
       </c>
       <c r="N6" t="n">
-        <v>4.7425</v>
+        <v>4.98</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>0.19875</v>
+        <v>0.2225</v>
       </c>
       <c r="N7" t="n">
-        <v>3.90375</v>
+        <v>4.152499999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>0.185</v>
+        <v>0.21125</v>
       </c>
       <c r="N8" t="n">
-        <v>4.142499999999999</v>
+        <v>4.40875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.17875</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3075</v>
+        <v>3.307499999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1899,10 +1899,10 @@
         <v>0.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06000000000000001</v>
+        <v>0.05999999999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>2.45375</v>
+        <v>2.453749999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.26625</v>
       </c>
       <c r="N13" t="n">
-        <v>5.25125</v>
+        <v>5.251249999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6449</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5627</v>
+      </c>
+      <c r="E75" t="n">
+        <v>822</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="G75" t="n">
+        <v>552</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.56%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>90</v>
+      </c>
+      <c r="J75" t="n">
+        <v>642</v>
+      </c>
+      <c r="K75" t="n">
+        <v>507</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.57875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.67125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2100000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3684210526315792</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.130000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2007540056550425</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.220000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2110266159695817</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
